--- a/news_daily/2026-10-01.xlsx
+++ b/news_daily/2026-10-01.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,12 +57,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE0B2"/>
+        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
+        <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,13 +89,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BL7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -829,6 +833,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -860,32 +884,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>反壟斷調查</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -925,7 +949,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>ANTITRUST_INVESTIGATION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -938,7 +962,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>b3b5e059acb9481283ff2ee59c83cfd1</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>eaeff46bbd8c10beb88f49e8</t>
@@ -965,7 +993,7 @@
       <c r="AN2" s="2" t="inlineStr"/>
       <c r="AO2" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" s="2" t="inlineStr"/>
@@ -1007,6 +1035,22 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1185,516 +1229,552 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>FDX</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>FedEx</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2026-10-01T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>CMA CGM Group completes acquisition of FedEx Supply Chain, strengthening its logistics presence in North America, and enters into multi-year commercial agreements related to air and ocean freight</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>一般公司更新</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0.935</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>人工覆核優先</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPRWQzWWFFWG1aT1ZQZldQdXVPam9zNVJpSHhRcUZtQV93VDJHMG9WTlpDLWJ5X2JWNzhYUXFOSTJLajh2d1pudXRhLWE3M05pSzA1OERoazRWajZxSi1NQ2lLQkRoRFU1V0lwV2VNOExfT0g2TldnWXZGX1ZVa3E4Y3hFZkZnbXRTWHM1V05RWWltbHRSUW52QXRPSW9PMzZxWExzZC1vLWtYUEZPanN1X2xPRm1NSzBhdmZtcWh6bDFSbEE?oc=5</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>CMA CGM Group</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>SUPPLY_CHAIN_DISRUPTION</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>supply chain</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>cca763560d252d49505a1636</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AD4" s="2" t="inlineStr">
         <is>
           <t>2ffb51a927beed95715fac74</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AE4" s="2" t="inlineStr">
         <is>
           <t>FDX-SUPPLY_CHAIN_DISRUPTION-001</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr"/>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr"/>
-      <c r="BC4" s="4" t="inlineStr">
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AK4" s="2" t="inlineStr"/>
+      <c r="AL4" s="2" t="inlineStr"/>
+      <c r="AM4" s="2" t="inlineStr"/>
+      <c r="AN4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AP4" s="2" t="inlineStr"/>
+      <c r="AQ4" s="2" t="inlineStr"/>
+      <c r="AR4" s="2" t="inlineStr"/>
+      <c r="AS4" s="2" t="inlineStr"/>
+      <c r="AT4" s="2" t="inlineStr"/>
+      <c r="AU4" s="2" t="inlineStr"/>
+      <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" s="2" t="inlineStr"/>
+      <c r="AX4" s="2" t="inlineStr"/>
+      <c r="AY4" s="2" t="inlineStr"/>
+      <c r="AZ4" s="2" t="inlineStr"/>
+      <c r="BA4" s="2" t="inlineStr"/>
+      <c r="BB4" s="2" t="inlineStr"/>
+      <c r="BC4" s="2" t="inlineStr">
         <is>
           <t>人工確認</t>
         </is>
       </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr"/>
-      <c r="BF4" s="4" t="inlineStr"/>
-      <c r="BG4" s="4" t="inlineStr"/>
-      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BD4" s="2" t="inlineStr"/>
+      <c r="BE4" s="2" t="inlineStr"/>
+      <c r="BF4" s="2" t="inlineStr"/>
+      <c r="BG4" s="2" t="inlineStr"/>
+      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>BALL</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Ball Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-10-01T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>‘Ball and chain’: Trump's tariffs still a drag on global trade cooperation</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>關稅</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>'-0.752</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPcnpwME1nQm5DcFBWTkZhWGpBelIyd1h6azdOSjNFNkMxaXQtMEVLUDVNVmtQS1JqM2djQmp1WllNc3RxMy1TcEphNEJvaFlFaHN4dFgtUGhPa2FUaTRELWhYWDQ2TVRiczhmMElid2l3NEdHWUpkNHU4OUtZdXJKQ3QwTkpIdw?oc=5</t>
         </is>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Politico</t>
         </is>
       </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>GEOPOLITICAL</t>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>TARIFF</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>tariff</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>a09c67d6c156dfdf791148cc</t>
         </is>
       </c>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AD5" s="2" t="inlineStr">
         <is>
           <t>b36a7a0c99b53c9f3b6c6bd4</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AE5" s="2" t="inlineStr">
         <is>
           <t>BALL-TARIFF-001</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr">
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr">
         <is>
           <t>BALL</t>
         </is>
       </c>
-      <c r="BC5" s="4" t="inlineStr">
+      <c r="BC5" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr">
+      <c r="BD5" s="2" t="inlineStr"/>
+      <c r="BE5" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="4" t="inlineStr">
+      <c r="BF5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="4" t="inlineStr">
+      <c r="BG5" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>PFE</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Pfizer, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>2026-10-01T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Florida Attorney General sues Pfizer and CEO over COVID-19 vaccine claims</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>'-0.923</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQSGtqMHRpcmY1UWVaczlyVThzd194ZXB0cC1rZUpheEZ5QTdRcjZUYjNXTjUtVmRiQjZ0Rk8xM3VaZTREMHFVRHVwMjdZOE4wZkQ3U1d3Z1JEcFgzWlNkQnZyNzc5UkZ0TkpXYkRsOHBuVGRMaFBudXF6MlBLYUpPcUxlU3R6Yno0bW5Pd2lFMkVPNGJHU1dNbzVWR2hTS0RfUnphd0tvWkRKdW9DU1ZVSjQxUkhJUkhuRk5sUUh3UGI3ekhyQ05CeUM2MUVINXd3dkZaYzhHX2k?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>attorney general</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>6f67700b652841a89f53bde489129a1e</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>450e6f549b37510611a63d91</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>87b832be833919af16679865</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr">
+        <is>
+          <t>PFE-MAJOR_LITIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>'-0.923</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQSGtqMHRpcmY1UWVaczlyVThzd194ZXB0cC1rZUpheEZ5QTdRcjZUYjNXTjUtVmRiQjZ0Rk8xM3VaZTREMHFVRHVwMjdZOE4wZkQ3U1d3Z1JEcFgzWlNkQnZyNzc5UkZ0TkpXYkRsOHBuVGRMaFBudXF6MlBLYUpPcUxlU3R6Yno0bW5Pd2lFMkVPNGJHU1dNbzVWR2hTS0RfUnphd0tvWkRKdW9DU1ZVSjQxUkhJUkhuRk5sUUh3UGI3ekhyQ05CeUM2MUVINXd3dkZaYzhHX2k?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>attorney general</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>450e6f549b37510611a63d91</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>87b832be833919af16679865</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr">
-        <is>
-          <t>PFE-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
         <is>
           <t>PFE</t>
         </is>
       </c>
-      <c r="BC6" s="2" t="inlineStr">
+      <c r="BC6" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="2" t="inlineStr"/>
-      <c r="BE6" s="2" t="inlineStr">
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="2" t="inlineStr">
+      <c r="BF6" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="2" t="inlineStr">
+      <c r="BG6" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1865,9 +1945,13 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH7"/>
+  <autoFilter ref="A1:BL7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1878,7 +1962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1941,6 +2025,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2244,713 +2332,587 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Otis Worldwide</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01T19:05:07+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>據消息人士稱，芬蘭通力公司正準備出售TK Elevator的歐洲業務，以應對反壟斷方面的擔憂</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>FDX</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>FedEx Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>CMA CGM finalizes $1.4B acquisition of FedEx Supply Chain</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>供應鏈中斷</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.091</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-OTIS/news/</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>反壟斷</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>0.068</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPZTlWU3VmNUpNZXBKY0g1elhreGFIVVNmTW1DZjRPWTM5aHFTblNtcW40bDFzNkw5VUthcmJCY3RmOUg0ZDZGVVJiMG1BMlptMmVmc3dyZExseTBBWDRDeEdYUlJYOXRqem5HUmdGc3YtTW95MWFHSk9mbklua1M3RTRscDkwaDNESkVmMTIxYXdOUm1X?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>FreightWaves</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>SUPPLY_CHAIN_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>eaeff46bbd8c10beb88f49e8</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>10c9afdbb65f9a4554453d23</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>OTIS-ANTITRUST_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>OTIS</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>OTIS</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>07ccb10db43b0adcbb049e40</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>3948a67a212811849cc68072</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr">
+        <is>
+          <t>FDX-SUPPLY_CHAIN_DISRUPTION-001</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr"/>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>FDX</t>
+        </is>
+      </c>
+      <c r="BC2" s="3" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD2" s="3" t="inlineStr"/>
+      <c r="BE2" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF2" s="2" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BG2" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>FDX</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>FedEx Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Pfizer, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>2026-10-01T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>CMA CGM finalizes $1.4B acquisition of FedEx Supply Chain</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Florida Attorney General sues Pfizer and CEO over COVID-19 vaccine claims</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>'-0.923</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQSGtqMHRpcmY1UWVaczlyVThzd194ZXB0cC1rZUpheEZ5QTdRcjZUYjNXTjUtVmRiQjZ0Rk8xM3VaZTREMHFVRHVwMjdZOE4wZkQ3U1d3Z1JEcFgzWlNkQnZyNzc5UkZ0TkpXYkRsOHBuVGRMaFBudXF6MlBLYUpPcUxlU3R6Yno0bW5Pd2lFMkVPNGJHU1dNbzVWR2hTS0RfUnphd0tvWkRKdW9DU1ZVSjQxUkhJUkhuRk5sUUh3UGI3ekhyQ05CeUM2MUVINXd3dkZaYzhHX2k?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>attorney general</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>6f67700b652841a89f53bde489129a1e</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>450e6f549b37510611a63d91</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>87b832be833919af16679865</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>PFE-MAJOR_LITIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
+      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AM3" s="4" t="inlineStr"/>
+      <c r="AN3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>0.068</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPZTlWU3VmNUpNZXBKY0g1elhreGFIVVNmTW1DZjRPWTM5aHFTblNtcW40bDFzNkw5VUthcmJCY3RmOUg0ZDZGVVJiMG1BMlptMmVmc3dyZExseTBBWDRDeEdYUlJYOXRqem5HUmdGc3YtTW95MWFHSk9mbklua1M3RTRscDkwaDNESkVmMTIxYXdOUm1X?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>FreightWaves</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>07ccb10db43b0adcbb049e40</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>3948a67a212811849cc68072</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr">
-        <is>
-          <t>FDX-SUPPLY_CHAIN_DISRUPTION-001</t>
-        </is>
-      </c>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AP3" s="4" t="inlineStr"/>
+      <c r="AQ3" s="4" t="inlineStr"/>
+      <c r="AR3" s="4" t="inlineStr"/>
+      <c r="AS3" s="4" t="inlineStr"/>
+      <c r="AT3" s="4" t="inlineStr"/>
+      <c r="AU3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>FDX</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="AX3" s="4" t="inlineStr"/>
+      <c r="AY3" s="4" t="inlineStr"/>
+      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="BC3" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BD3" s="4" t="inlineStr"/>
+      <c r="BE3" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr">
+      <c r="BF3" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BG3" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Pfizer, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2026-10-01T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Florida Attorney General sues Pfizer and CEO over COVID-19 vaccine claims</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Paramount-WBD Deal Architect Gerry Cardinale Says Most Of $6B In Expected Cost Savings Will Not Be From Layoffs</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>'-0.923</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>'-0.097</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQSGtqMHRpcmY1UWVaczlyVThzd194ZXB0cC1rZUpheEZ5QTdRcjZUYjNXTjUtVmRiQjZ0Rk8xM3VaZTREMHFVRHVwMjdZOE4wZkQ3U1d3Z1JEcFgzWlNkQnZyNzc5UkZ0TkpXYkRsOHBuVGRMaFBudXF6MlBLYUpPcUxlU3R6Yno0bW5Pd2lFMkVPNGJHU1dNbzVWR2hTS0RfUnphd0tvWkRKdW9DU1ZVSjQxUkhJUkhuRk5sUUh3UGI3ekhyQ05CeUM2MUVINXd3dkZaYzhHX2k?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>attorney general</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPS3YwSzZkQTBhYzd0bEZuVVlfdDZZTFpfc1R3a3Z4UmUwcm1XWUpFc05FM1RlVTUwZ2ZEY2c5OGxDNzE5bElSNzBpVXBJek5UZE5aZm53Ml9HSkxtZzRFUllMSkt5UHBFM3UzWW5BRFNZemI5SW1NRGdHNVQ2TFBtQ0EzUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>450e6f549b37510611a63d91</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>87b832be833919af16679865</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr">
-        <is>
-          <t>PFE-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="BC4" s="2" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>7cb41762fcab37482e085e26</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>91e6abfabe8f86e53c6a1948</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>WBD-WORKFORCE_REDUCTION-001</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr"/>
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Paramount-WBD Deal Architect Gerry Cardinale Says Most Of $6B In Expected Cost Savings Will Not Be From Layoffs</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>'-0.097</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPS3YwSzZkQTBhYzd0bEZuVVlfdDZZTFpfc1R3a3Z4UmUwcm1XWUpFc05FM1RlVTUwZ2ZEY2c5OGxDNzE5bElSNzBpVXBJek5UZE5aZm53Ml9HSkxtZzRFUllMSkt5UHBFM3UzWW5BRFNZemI5SW1NRGdHNVQ2TFBtQ0EzUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>7cb41762fcab37482e085e26</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>91e6abfabe8f86e53c6a1948</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr">
-        <is>
-          <t>WBD-WORKFORCE_REDUCTION-001</t>
-        </is>
-      </c>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr"/>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="BC5" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF5" s="3" t="inlineStr"/>
-      <c r="BG5" s="3" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH5"/>
+  <autoFilter ref="A1:BL4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2961,7 +2923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH2"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3024,6 +2986,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3327,187 +3293,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Otis Worldwide</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01T19:05:07+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>據消息人士稱，芬蘭通力公司正準備出售TK Elevator的歐洲業務，以應對反壟斷方面的擔憂</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.091</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-OTIS/news/</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>反壟斷</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>eaeff46bbd8c10beb88f49e8</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>10c9afdbb65f9a4554453d23</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>OTIS-ANTITRUST_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>OTIS</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>OTIS</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH2"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3518,7 +3326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3581,6 +3389,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3884,9 +3696,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3897,7 +3729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3947,477 +3779,768 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>ticker-audit-20261024-081549</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ticker-audit</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="4" t="n">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="4" t="inlineStr"/>
-      <c r="AA2" s="4" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-25</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="b">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="R3" s="4" t="n">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>2089</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="n">
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="Z3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="V3" s="2" t="n">
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-24</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="n">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>3802</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ticker-audit-20261024-081549</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ticker-audit</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="n">
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="n">
+      <c r="M8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="b">
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="R5" s="4" t="n">
+      <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="4" t="n">
+      <c r="W8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-10-01.xlsx
+++ b/news_daily/2026-10-01.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -93,9 +88,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1053,186 +1045,210 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>FDX</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>FedEx Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-10-01T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>CMA CGM finalizes $1.4B acquisition of FedEx Supply Chain</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>0.068</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPZTlWU3VmNUpNZXBKY0g1elhreGFIVVNmTW1DZjRPWTM5aHFTblNtcW40bDFzNkw5VUthcmJCY3RmOUg0ZDZGVVJiMG1BMlptMmVmc3dyZExseTBBWDRDeEdYUlJYOXRqem5HUmdGc3YtTW95MWFHSk9mbklua1M3RTRscDkwaDNESkVmMTIxYXdOUm1X?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>FreightWaves</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>81752818392142949be86ac296b58bd0</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>07ccb10db43b0adcbb049e40</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>3948a67a212811849cc68072</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>FDX-SUPPLY_CHAIN_DISRUPTION-001</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>0.068</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPZTlWU3VmNUpNZXBKY0g1elhreGFIVVNmTW1DZjRPWTM5aHFTblNtcW40bDFzNkw5VUthcmJCY3RmOUg0ZDZGVVJiMG1BMlptMmVmc3dyZExseTBBWDRDeEdYUlJYOXRqem5HUmdGc3YtTW95MWFHSk9mbklua1M3RTRscDkwaDNESkVmMTIxYXdOUm1X?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>FreightWaves</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>07ccb10db43b0adcbb049e40</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>3948a67a212811849cc68072</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr">
-        <is>
-          <t>FDX-SUPPLY_CHAIN_DISRUPTION-001</t>
-        </is>
-      </c>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr"/>
+      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
+      <c r="AX3" s="2" t="inlineStr"/>
+      <c r="AY3" s="2" t="inlineStr"/>
+      <c r="AZ3" s="2" t="inlineStr"/>
+      <c r="BA3" s="2" t="inlineStr"/>
+      <c r="BB3" s="2" t="inlineStr">
         <is>
           <t>FDX</t>
         </is>
       </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="BC3" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BD3" s="2" t="inlineStr"/>
+      <c r="BE3" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr">
+      <c r="BF3" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BG3" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
-      <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1575,380 +1591,404 @@
       <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>PFE</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Pfizer, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>2026-10-01T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Florida Attorney General sues Pfizer and CEO over COVID-19 vaccine claims</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>'-0.923</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQSGtqMHRpcmY1UWVaczlyVThzd194ZXB0cC1rZUpheEZ5QTdRcjZUYjNXTjUtVmRiQjZ0Rk8xM3VaZTREMHFVRHVwMjdZOE4wZkQ3U1d3Z1JEcFgzWlNkQnZyNzc5UkZ0TkpXYkRsOHBuVGRMaFBudXF6MlBLYUpPcUxlU3R6Yno0bW5Pd2lFMkVPNGJHU1dNbzVWR2hTS0RfUnphd0tvWkRKdW9DU1ZVSjQxUkhJUkhuRk5sUUh3UGI3ekhyQ05CeUM2MUVINXd3dkZaYzhHX2k?oc=5</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t>Reuters</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>MAJOR_LITIGATION</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>attorney general</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>6f67700b652841a89f53bde489129a1e</t>
         </is>
       </c>
-      <c r="AC6" s="4" t="inlineStr">
+      <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>450e6f549b37510611a63d91</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AD6" s="3" t="inlineStr">
         <is>
           <t>87b832be833919af16679865</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>PFE-MAJOR_LITIGATION-001</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr">
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
         <is>
           <t>PFE</t>
         </is>
       </c>
-      <c r="BC6" s="4" t="inlineStr">
+      <c r="BC6" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="4" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="4" t="inlineStr">
+      <c r="BG6" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="4" t="inlineStr"/>
-      <c r="BI6" s="4" t="inlineStr"/>
-      <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr">
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL6" s="4" t="inlineStr">
+      <c r="BL6" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>WBD</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Warner Bros. Discovery</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-10-01T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Paramount-WBD Deal Architect Gerry Cardinale Says Most Of $6B In Expected Cost Savings Will Not Be From Layoffs</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>'-0.097</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPS3YwSzZkQTBhYzd0bEZuVVlfdDZZTFpfc1R3a3Z4UmUwcm1XWUpFc05FM1RlVTUwZ2ZEY2c5OGxDNzE5bElSNzBpVXBJek5UZE5aZm53Ml9HSkxtZzRFUllMSkt5UHBFM3UzWW5BRFNZemI5SW1NRGdHNVQ2TFBtQ0EzUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>d849841ca4154cbc9e5da7d0492987a9</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>7cb41762fcab37482e085e26</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>91e6abfabe8f86e53c6a1948</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>WBD-WORKFORCE_REDUCTION-001</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr"/>
+      <c r="AL7" s="2" t="inlineStr"/>
+      <c r="AM7" s="2" t="inlineStr"/>
+      <c r="AN7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>'-0.097</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPS3YwSzZkQTBhYzd0bEZuVVlfdDZZTFpfc1R3a3Z4UmUwcm1XWUpFc05FM1RlVTUwZ2ZEY2c5OGxDNzE5bElSNzBpVXBJek5UZE5aZm53Ml9HSkxtZzRFUllMSkt5UHBFM3UzWW5BRFNZemI5SW1NRGdHNVQ2TFBtQ0EzUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>7cb41762fcab37482e085e26</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>91e6abfabe8f86e53c6a1948</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr">
-        <is>
-          <t>WBD-WORKFORCE_REDUCTION-001</t>
-        </is>
-      </c>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr"/>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
+      <c r="AP7" s="2" t="inlineStr"/>
+      <c r="AQ7" s="2" t="inlineStr"/>
+      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AS7" s="2" t="inlineStr"/>
+      <c r="AT7" s="2" t="inlineStr"/>
+      <c r="AU7" s="2" t="inlineStr"/>
+      <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" s="2" t="inlineStr"/>
+      <c r="AX7" s="2" t="inlineStr"/>
+      <c r="AY7" s="2" t="inlineStr"/>
+      <c r="AZ7" s="2" t="inlineStr"/>
+      <c r="BA7" s="2" t="inlineStr"/>
+      <c r="BB7" s="2" t="inlineStr">
         <is>
           <t>WBD</t>
         </is>
       </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="BC7" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BD7" s="2" t="inlineStr"/>
+      <c r="BE7" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF7" s="3" t="inlineStr"/>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BF7" s="2" t="inlineStr"/>
+      <c r="BG7" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL7"/>
@@ -1962,7 +2002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL4"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2366,12 +2406,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>FedEx Corporation Common Stock</t>
+          <t>Pfizer, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -2381,34 +2421,38 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>CMA CGM finalizes $1.4B acquisition of FedEx Supply Chain</t>
+          <t>Florida Attorney General sues Pfizer and CEO over COVID-19 vaccine claims</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>供應鏈中斷</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -2418,7 +2462,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>'-0.923</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr"/>
@@ -2432,28 +2476,28 @@
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPZTlWU3VmNUpNZXBKY0g1elhreGFIVVNmTW1DZjRPWTM5aHFTblNtcW40bDFzNkw5VUthcmJCY3RmOUg0ZDZGVVJiMG1BMlptMmVmc3dyZExseTBBWDRDeEdYUlJYOXRqem5HUmdGc3YtTW95MWFHSk9mbklua1M3RTRscDkwaDNESkVmMTIxYXdOUm1X?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQSGtqMHRpcmY1UWVaczlyVThzd194ZXB0cC1rZUpheEZ5QTdRcjZUYjNXTjUtVmRiQjZ0Rk8xM3VaZTREMHFVRHVwMjdZOE4wZkQ3U1d3Z1JEcFgzWlNkQnZyNzc5UkZ0TkpXYkRsOHBuVGRMaFBudXF6MlBLYUpPcUxlU3R6Yno0bW5Pd2lFMkVPNGJHU1dNbzVWR2hTS0RfUnphd0tvWkRKdW9DU1ZVSjQxUkhJUkhuRk5sUUh3UGI3ekhyQ05CeUM2MUVINXd3dkZaYzhHX2k?oc=5</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>FreightWaves</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr"/>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>LEGAL</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>supply chain</t>
+          <t>attorney general</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr">
@@ -2461,20 +2505,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>6f67700b652841a89f53bde489129a1e</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
-          <t>07ccb10db43b0adcbb049e40</t>
+          <t>450e6f549b37510611a63d91</t>
         </is>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>3948a67a212811849cc68072</t>
+          <t>87b832be833919af16679865</t>
         </is>
       </c>
       <c r="AE2" s="3" t="inlineStr">
         <is>
-          <t>FDX-SUPPLY_CHAIN_DISRUPTION-001</t>
+          <t>PFE-MAJOR_LITIGATION-001</t>
         </is>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
@@ -2486,7 +2534,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -2505,7 +2557,7 @@
       <c r="BA2" s="3" t="inlineStr"/>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="BC2" s="3" t="inlineStr">
@@ -2532,387 +2584,19 @@
       <c r="BH2" s="3" t="inlineStr"/>
       <c r="BI2" s="3" t="inlineStr"/>
       <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Pfizer, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Florida Attorney General sues Pfizer and CEO over COVID-19 vaccine claims</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>'-0.923</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQSGtqMHRpcmY1UWVaczlyVThzd194ZXB0cC1rZUpheEZ5QTdRcjZUYjNXTjUtVmRiQjZ0Rk8xM3VaZTREMHFVRHVwMjdZOE4wZkQ3U1d3Z1JEcFgzWlNkQnZyNzc5UkZ0TkpXYkRsOHBuVGRMaFBudXF6MlBLYUpPcUxlU3R6Yno0bW5Pd2lFMkVPNGJHU1dNbzVWR2hTS0RfUnphd0tvWkRKdW9DU1ZVSjQxUkhJUkhuRk5sUUh3UGI3ekhyQ05CeUM2MUVINXd3dkZaYzhHX2k?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>attorney general</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="4" t="inlineStr">
-        <is>
-          <t>6f67700b652841a89f53bde489129a1e</t>
-        </is>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>450e6f549b37510611a63d91</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>87b832be833919af16679865</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr">
-        <is>
-          <t>PFE-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="inlineStr"/>
-      <c r="AR3" s="4" t="inlineStr"/>
-      <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="inlineStr"/>
-      <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX3" s="4" t="inlineStr"/>
-      <c r="AY3" s="4" t="inlineStr"/>
-      <c r="AZ3" s="4" t="inlineStr"/>
-      <c r="BA3" s="4" t="inlineStr"/>
-      <c r="BB3" s="4" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="BC3" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD3" s="4" t="inlineStr"/>
-      <c r="BE3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH3" s="4" t="inlineStr"/>
-      <c r="BI3" s="4" t="inlineStr"/>
-      <c r="BJ3" s="4" t="inlineStr"/>
-      <c r="BK3" s="4" t="inlineStr">
+      <c r="BK2" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL3" s="4" t="inlineStr">
+      <c r="BL2" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-01T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Paramount-WBD Deal Architect Gerry Cardinale Says Most Of $6B In Expected Cost Savings Will Not Be From Layoffs</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>'-0.097</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPS3YwSzZkQTBhYzd0bEZuVVlfdDZZTFpfc1R3a3Z4UmUwcm1XWUpFc05FM1RlVTUwZ2ZEY2c5OGxDNzE5bElSNzBpVXBJek5UZE5aZm53Ml9HSkxtZzRFUllMSkt5UHBFM3UzWW5BRFNZemI5SW1NRGdHNVQ2TFBtQ0EzUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>7cb41762fcab37482e085e26</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>91e6abfabe8f86e53c6a1948</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>WBD-WORKFORCE_REDUCTION-001</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr"/>
-      <c r="AG4" s="3" t="inlineStr"/>
-      <c r="AH4" s="3" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr"/>
-      <c r="AJ4" s="3" t="inlineStr"/>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr"/>
-      <c r="AX4" s="3" t="inlineStr"/>
-      <c r="AY4" s="3" t="inlineStr"/>
-      <c r="AZ4" s="3" t="inlineStr"/>
-      <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD4" s="3" t="inlineStr"/>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr"/>
-      <c r="BG4" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH4" s="3" t="inlineStr"/>
-      <c r="BI4" s="3" t="inlineStr"/>
-      <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
-      <c r="BL4" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL4"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-10-01.xlsx
+++ b/news_daily/2026-10-01.xlsx
@@ -1442,28 +1442,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1503,7 +1507,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1516,7 +1520,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>ab03c3e765bc4ada81e6d63a47f0af6e</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>a09c67d6c156dfdf791148cc</t>
@@ -1541,7 +1549,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1585,10 +1597,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">

--- a/news_daily/2026-10-01.xlsx
+++ b/news_daily/2026-10-01.xlsx
@@ -1282,10 +1282,14 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>一般公司更新</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1298,7 +1302,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1341,7 +1349,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1354,7 +1362,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>676173aa7e1d4b1b98bcf8627a1ad935</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>cca763560d252d49505a1636</t>
@@ -1379,7 +1391,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1403,10 +1419,22 @@
       <c r="BF4" s="2" t="inlineStr"/>
       <c r="BG4" s="2" t="inlineStr"/>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
